--- a/actividadAvances.xlsx
+++ b/actividadAvances.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Carpeta de proyectos de la une\backend_base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1299699-2D18-4F95-ABCB-A44F591D758F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61A0018-714D-4D82-8DD2-3F13597AF8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{684B1366-1166-4188-8B1E-CEDD8DE4EB6A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{684B1366-1166-4188-8B1E-CEDD8DE4EB6A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="VARIABLES" sheetId="1" r:id="rId1"/>
+    <sheet name="HORAS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>actividad</t>
   </si>
@@ -83,9 +84,6 @@
     <t>periodos</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>idperiodos,per_nombre,per_activa,per_mostrar</t>
   </si>
   <si>
@@ -111,6 +109,60 @@
   </si>
   <si>
     <t>idprofesores, pro_apellidosNombres, pro_cedula, pro_email, pro_password, pro_tipo, pro_sexo, pro_categoria, pro_titulo_tercer, pro_titulo_cuarto, pro_tipo_cuarto, rol</t>
+  </si>
+  <si>
+    <t>todos</t>
+  </si>
+  <si>
+    <t>dos</t>
+  </si>
+  <si>
+    <t>tres</t>
+  </si>
+  <si>
+    <t>Presentacion de tema</t>
+  </si>
+  <si>
+    <t>Idea del Modelo q preparar</t>
+  </si>
+  <si>
+    <t>Realizacion   de el Login y Profesores</t>
+  </si>
+  <si>
+    <t>Realizacion de dashboar y periodo</t>
+  </si>
+  <si>
+    <t>preparacion y rescriccion de codigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reunion para hagregar  propuestas e ideas </t>
+  </si>
+  <si>
+    <t>Planificacion y correcion de analizis  y demanda</t>
+  </si>
+  <si>
+    <t>Actividades Realizadas</t>
+  </si>
+  <si>
+    <t>Divición de tareas</t>
+  </si>
+  <si>
+    <t>miercoles</t>
+  </si>
+  <si>
+    <t>viernes</t>
+  </si>
+  <si>
+    <t>martes</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>S-8:30A 10:30</t>
+  </si>
+  <si>
+    <t>HORA</t>
   </si>
 </sst>
 </file>
@@ -141,15 +193,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -172,11 +236,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -191,6 +264,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,8 +616,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="35.88671875" customWidth="1"/>
+    <col min="4" max="4" width="44.109375" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -554,7 +641,7 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -570,7 +657,7 @@
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -586,7 +673,7 @@
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -602,7 +689,7 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -618,7 +705,7 @@
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -634,7 +721,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -650,7 +737,7 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -662,11 +749,11 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -684,7 +771,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -822,4 +909,454 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9F69E51-8261-4ACE-9A06-EA6C22762B6C}">
+  <dimension ref="A2:N23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>12</v>
+      </c>
+      <c r="B4" s="5">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5">
+        <v>18</v>
+      </c>
+      <c r="E4" s="7">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7">
+        <v>26</v>
+      </c>
+      <c r="G4" s="5">
+        <v>29</v>
+      </c>
+      <c r="H4" s="7">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5">
+        <v>5</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <f>SUM(A7:H7)</f>
+        <v>25</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/actividadAvances.xlsx
+++ b/actividadAvances.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Carpeta de proyectos de la une\backend_base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61A0018-714D-4D82-8DD2-3F13597AF8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380B193F-75AA-4517-A436-28A5D89267E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{684B1366-1166-4188-8B1E-CEDD8DE4EB6A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{684B1366-1166-4188-8B1E-CEDD8DE4EB6A}"/>
   </bookViews>
   <sheets>
     <sheet name="VARIABLES" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
   <si>
     <t>actividad</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t>HORA</t>
+  </si>
+  <si>
+    <t>uno</t>
+  </si>
+  <si>
+    <t>Separar la rutas y  tener tres archivos modelos controlador y rutas</t>
   </si>
 </sst>
 </file>
@@ -272,11 +278,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -925,11 +931,11 @@
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="10"/>
       <c r="I2" s="9"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -957,7 +963,9 @@
       <c r="H3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>36</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -989,7 +997,9 @@
       <c r="H4" s="7">
         <v>3</v>
       </c>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1">
+        <v>7</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1021,14 +1031,16 @@
       <c r="H5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>27</v>
       </c>
@@ -1053,7 +1065,9 @@
       <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1085,7 +1099,9 @@
       <c r="H7" s="5">
         <v>2</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <v>4.3</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1110,8 +1126,8 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <f>SUM(A7:H7)</f>
-        <v>25</v>
+        <f>SUM(A7:I7)</f>
+        <v>29.3</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>41</v>
